--- a/evidence/pg16_recovery_before_2.xlsx
+++ b/evidence/pg16_recovery_before_2.xlsx
@@ -78,7 +78,7 @@
     <t>snapshot_id</t>
   </si>
   <si>
-    <t>76ece24ad0759909318c82b175d388f4</t>
+    <t>a90465869c529e00c05a4519e5a5199c</t>
   </si>
   <si>
     <t>integration_id</t>
@@ -114,19 +114,19 @@
     <t>source_watermark</t>
   </si>
   <si>
-    <t>fixture-b1346103b2c666a20810c7cb7787b1d9</t>
+    <t>fixture-6532f31877572f3f06077b84a1f695a5</t>
   </si>
   <si>
     <t>source_snapshot_ref</t>
   </si>
   <si>
-    <t>1da242e45be7b43a4ac9902c018df801</t>
+    <t>188889a07e4b87d24ad36175a262f56c</t>
   </si>
   <si>
     <t>expires_at</t>
   </si>
   <si>
-    <t>2026-10-26T07:06:08Z</t>
+    <t>2026-10-26T07:30:21Z</t>
   </si>
   <si>
     <t>precision</t>
